--- a/R/inst/extdata/cox_threshold_results.xlsx
+++ b/R/inst/extdata/cox_threshold_results.xlsx
@@ -24,7 +24,7 @@
     <t xml:space="preserve">Cutoff</t>
   </si>
   <si>
-    <t xml:space="preserve">SBP</t>
+    <t xml:space="preserve">SOFA_CRRT_0h</t>
   </si>
   <si>
     <t xml:space="preserve">HR</t>
@@ -405,7 +405,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>131</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -441,16 +441,16 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.982299929217888</v>
+        <v>1.17866921584805</v>
       </c>
       <c r="C2" t="n">
-        <v>0.976535020944213</v>
+        <v>1.151522336296</v>
       </c>
       <c r="D2" t="n">
-        <v>0.988098870236617</v>
+        <v>1.20645607696727</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00000000273752529825406</v>
+        <v>0.000000000000000000000000000000000000000000174628078726173</v>
       </c>
     </row>
     <row r="3">
@@ -458,16 +458,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>1.00288404865869</v>
+        <v>1.00695690845639</v>
       </c>
       <c r="C3" t="n">
-        <v>0.994863204961461</v>
+        <v>1.00157819257622</v>
       </c>
       <c r="D3" t="n">
-        <v>1.01096955846608</v>
+        <v>1.01236450933499</v>
       </c>
       <c r="E3" t="n">
-        <v>0.482098119887636</v>
+        <v>0.0111793171796471</v>
       </c>
     </row>
     <row r="4">
@@ -475,16 +475,16 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>1.04861569986881</v>
+        <v>1.04284636912299</v>
       </c>
       <c r="C4" t="n">
-        <v>0.825878506564424</v>
+        <v>0.894947650568465</v>
       </c>
       <c r="D4" t="n">
-        <v>1.33142451010811</v>
+        <v>1.21518677534067</v>
       </c>
       <c r="E4" t="n">
-        <v>0.696791559587187</v>
+        <v>0.59082876757865</v>
       </c>
     </row>
   </sheetData>
@@ -520,16 +520,16 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>1.02039963292243</v>
+        <v>0.72173250984932</v>
       </c>
       <c r="C2" t="n">
-        <v>1.01286794902822</v>
+        <v>0.558086599163062</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0279873224019</v>
+        <v>0.933363776436429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000000916493747338261</v>
+        <v>0.0129337005152244</v>
       </c>
     </row>
     <row r="3">
@@ -537,16 +537,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>0.993345233835617</v>
+        <v>1.17088901539722</v>
       </c>
       <c r="C3" t="n">
-        <v>0.971901493412469</v>
+        <v>1.14151739123445</v>
       </c>
       <c r="D3" t="n">
-        <v>1.01526210245792</v>
+        <v>1.20101638127063</v>
       </c>
       <c r="E3" t="n">
-        <v>0.548738184600624</v>
+        <v>0.000000000000000000000000000000000441992364103942</v>
       </c>
     </row>
     <row r="4">
@@ -554,16 +554,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>1.00272682142932</v>
+        <v>1.00674992732498</v>
       </c>
       <c r="C4" t="n">
-        <v>0.994706347720239</v>
+        <v>1.00136518527364</v>
       </c>
       <c r="D4" t="n">
-        <v>1.01081196547922</v>
+        <v>1.01216362529308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.506313310242132</v>
+        <v>0.0139501143292487</v>
       </c>
     </row>
     <row r="5">
@@ -571,16 +571,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>1.03834542978454</v>
+        <v>1.04286911700438</v>
       </c>
       <c r="C5" t="n">
-        <v>0.817242928330978</v>
+        <v>0.895023643106811</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3192665169417</v>
+        <v>1.2151366096054</v>
       </c>
       <c r="E5" t="n">
-        <v>0.758080006577317</v>
+        <v>0.590482494879723</v>
       </c>
     </row>
   </sheetData>
@@ -616,16 +616,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>1.0136091119711</v>
+        <v>0.84506866783764</v>
       </c>
       <c r="C2" t="n">
-        <v>0.987756370738966</v>
+        <v>0.648412569228227</v>
       </c>
       <c r="D2" t="n">
-        <v>1.04013850207033</v>
+        <v>1.10136830661826</v>
       </c>
       <c r="E2" t="n">
-        <v>0.30516150518096</v>
+        <v>0.212928821397565</v>
       </c>
     </row>
     <row r="3">
@@ -633,16 +633,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.98000819260979</v>
+        <v>1.38555487850862</v>
       </c>
       <c r="C3" t="n">
-        <v>0.972774642457162</v>
+        <v>1.07139362512854</v>
       </c>
       <c r="D3" t="n">
-        <v>0.987295531425822</v>
+        <v>1.79183661012423</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000000916493747338386</v>
+        <v>0.0129337005152626</v>
       </c>
     </row>
     <row r="4">
@@ -650,16 +650,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>1.00272682142932</v>
+        <v>1.00674992732498</v>
       </c>
       <c r="C4" t="n">
-        <v>0.994706347720239</v>
+        <v>1.00136518527364</v>
       </c>
       <c r="D4" t="n">
-        <v>1.01081196547922</v>
+        <v>1.01216362529308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.506313310242133</v>
+        <v>0.013950114329249</v>
       </c>
     </row>
     <row r="5">
@@ -667,16 +667,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>1.03834542978454</v>
+        <v>1.04286911700438</v>
       </c>
       <c r="C5" t="n">
-        <v>0.817242928330978</v>
+        <v>0.895023643106811</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3192665169417</v>
+        <v>1.2151366096054</v>
       </c>
       <c r="E5" t="n">
-        <v>0.758080006577317</v>
+        <v>0.590482494879723</v>
       </c>
     </row>
   </sheetData>
@@ -712,7 +712,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>-1610.06400024534</v>
+        <v>-4595.80212040475</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -723,16 +723,16 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>-1609.56952219475</v>
+        <v>-4594.91559449355</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.988956101179156</v>
+        <v>1.7730518223907</v>
       </c>
       <c r="E3" t="n">
-        <v>0.319997646381061</v>
+        <v>0.183004842515714</v>
       </c>
     </row>
   </sheetData>
